--- a/officepro_direccion.xlsx
+++ b/officepro_direccion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\code\_other\datos-officepro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DAEF2C-5539-48B5-8653-40432C7A17E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED07765E-2E3D-46F7-A6F2-6995A466D9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14145" yWindow="-16485" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14655" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetivos" sheetId="1" r:id="rId1"/>
@@ -363,20 +363,20 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,16 +680,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB121"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="15" width="8.88671875" style="1" customWidth="1"/>
-    <col min="16" max="28" width="8.88671875" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.88671875" style="1"/>
+    <col min="16" max="17" width="8.88671875" customWidth="1"/>
+    <col min="18" max="18" width="8.88671875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -740,10 +740,10 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20">
+      <c r="A2" s="17">
         <v>2023</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -787,8 +787,8 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="23"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
@@ -830,8 +830,8 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21"/>
-      <c r="B4" s="23"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
@@ -873,8 +873,8 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21"/>
-      <c r="B5" s="23"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
@@ -916,8 +916,8 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="23"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
@@ -959,8 +959,8 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1002,8 +1002,8 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="23"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1045,8 +1045,8 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="23"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1088,8 +1088,8 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="23"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1131,8 +1131,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="23"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
@@ -1174,8 +1174,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="23"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1217,8 +1217,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="23"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
@@ -1260,8 +1260,8 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="23"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
@@ -1303,8 +1303,8 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="23"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1346,8 +1346,8 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="18"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="13" t="s">
         <v>31</v>
       </c>
@@ -1389,8 +1389,8 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -1434,8 +1434,8 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="23"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1477,8 +1477,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1520,8 +1520,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
@@ -1563,8 +1563,8 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
-      <c r="B21" s="23"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
@@ -1606,8 +1606,8 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="23"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
@@ -1649,8 +1649,8 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="21"/>
-      <c r="B23" s="23"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1692,8 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
-      <c r="B24" s="23"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="1" t="s">
         <v>24</v>
       </c>
@@ -1735,8 +1735,8 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="21"/>
-      <c r="B25" s="23"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="1" t="s">
         <v>25</v>
       </c>
@@ -1778,8 +1778,8 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
-      <c r="B26" s="23"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="21"/>
       <c r="C26" s="1" t="s">
         <v>26</v>
       </c>
@@ -1821,8 +1821,8 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21"/>
-      <c r="B27" s="23"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="1" t="s">
         <v>27</v>
       </c>
@@ -1864,8 +1864,8 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="21"/>
-      <c r="B28" s="23"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
@@ -1907,8 +1907,8 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21"/>
-      <c r="B29" s="23"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
@@ -1950,8 +1950,8 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21"/>
-      <c r="B30" s="23"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
@@ -1993,8 +1993,8 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
-      <c r="B31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="13" t="s">
         <v>31</v>
       </c>
@@ -2036,10 +2036,10 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20">
+      <c r="A32" s="17">
         <v>2024</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -2083,8 +2083,8 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="21"/>
-      <c r="B33" s="23"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="21"/>
       <c r="C33" s="1" t="s">
         <v>18</v>
       </c>
@@ -2126,8 +2126,8 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="21"/>
-      <c r="B34" s="23"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="21"/>
       <c r="C34" s="1" t="s">
         <v>19</v>
       </c>
@@ -2169,8 +2169,8 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="21"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="21"/>
       <c r="C35" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,8 +2212,8 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="21"/>
-      <c r="B36" s="23"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="21"/>
       <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
@@ -2255,8 +2255,8 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="21"/>
-      <c r="B37" s="23"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="21"/>
       <c r="C37" s="1" t="s">
         <v>22</v>
       </c>
@@ -2298,8 +2298,8 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="21"/>
-      <c r="B38" s="23"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="21"/>
       <c r="C38" s="1" t="s">
         <v>23</v>
       </c>
@@ -2341,8 +2341,8 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="21"/>
-      <c r="B39" s="23"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="21"/>
       <c r="C39" s="1" t="s">
         <v>24</v>
       </c>
@@ -2384,8 +2384,8 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="21"/>
-      <c r="B40" s="23"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="21"/>
       <c r="C40" s="1" t="s">
         <v>25</v>
       </c>
@@ -2427,8 +2427,8 @@
       </c>
     </row>
     <row r="41" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="21"/>
-      <c r="B41" s="23"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="21"/>
       <c r="C41" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2470,8 @@
       </c>
     </row>
     <row r="42" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="21"/>
-      <c r="B42" s="23"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="21"/>
       <c r="C42" s="1" t="s">
         <v>27</v>
       </c>
@@ -2513,8 +2513,8 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21"/>
-      <c r="B43" s="23"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="21"/>
       <c r="C43" s="1" t="s">
         <v>28</v>
       </c>
@@ -2556,8 +2556,8 @@
       </c>
     </row>
     <row r="44" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="21"/>
-      <c r="B44" s="23"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="21"/>
       <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
@@ -2599,8 +2599,8 @@
       </c>
     </row>
     <row r="45" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="21"/>
-      <c r="B45" s="23"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="21"/>
       <c r="C45" s="1" t="s">
         <v>30</v>
       </c>
@@ -2642,8 +2642,8 @@
       </c>
     </row>
     <row r="46" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="21"/>
-      <c r="B46" s="18"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="22"/>
       <c r="C46" s="13" t="s">
         <v>31</v>
       </c>
@@ -2685,8 +2685,8 @@
       </c>
     </row>
     <row r="47" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="21"/>
-      <c r="B47" s="19" t="s">
+      <c r="A47" s="18"/>
+      <c r="B47" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -2730,8 +2730,8 @@
       </c>
     </row>
     <row r="48" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="21"/>
-      <c r="B48" s="23"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="21"/>
       <c r="C48" s="1" t="s">
         <v>18</v>
       </c>
@@ -2773,8 +2773,8 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="21"/>
-      <c r="B49" s="23"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="21"/>
       <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
@@ -2816,8 +2816,8 @@
       </c>
     </row>
     <row r="50" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="21"/>
-      <c r="B50" s="23"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="21"/>
       <c r="C50" s="1" t="s">
         <v>20</v>
       </c>
@@ -2859,8 +2859,8 @@
       </c>
     </row>
     <row r="51" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="21"/>
-      <c r="B51" s="23"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="21"/>
       <c r="C51" s="1" t="s">
         <v>21</v>
       </c>
@@ -2902,8 +2902,8 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21"/>
-      <c r="B52" s="23"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="21"/>
       <c r="C52" s="1" t="s">
         <v>22</v>
       </c>
@@ -2945,8 +2945,8 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21"/>
-      <c r="B53" s="23"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="1" t="s">
         <v>23</v>
       </c>
@@ -2988,8 +2988,8 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="23"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="21"/>
       <c r="C54" s="1" t="s">
         <v>24</v>
       </c>
@@ -3031,8 +3031,8 @@
       </c>
     </row>
     <row r="55" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="21"/>
       <c r="C55" s="1" t="s">
         <v>25</v>
       </c>
@@ -3074,8 +3074,8 @@
       </c>
     </row>
     <row r="56" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
-      <c r="B56" s="23"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="21"/>
       <c r="C56" s="1" t="s">
         <v>26</v>
       </c>
@@ -3117,8 +3117,8 @@
       </c>
     </row>
     <row r="57" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="1" t="s">
         <v>27</v>
       </c>
@@ -3160,8 +3160,8 @@
       </c>
     </row>
     <row r="58" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="1" t="s">
         <v>28</v>
       </c>
@@ -3203,8 +3203,8 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
-      <c r="B59" s="23"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="21"/>
       <c r="C59" s="1" t="s">
         <v>29</v>
       </c>
@@ -3246,8 +3246,8 @@
       </c>
     </row>
     <row r="60" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="21"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="21"/>
       <c r="C60" s="1" t="s">
         <v>30</v>
       </c>
@@ -3289,8 +3289,8 @@
       </c>
     </row>
     <row r="61" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="22"/>
-      <c r="B61" s="18"/>
+      <c r="A61" s="19"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="13" t="s">
         <v>31</v>
       </c>
@@ -3332,10 +3332,10 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="20">
+      <c r="A62" s="17">
         <v>2025</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -3379,8 +3379,8 @@
       </c>
     </row>
     <row r="63" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="21"/>
-      <c r="B63" s="23"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="21"/>
       <c r="C63" s="1" t="s">
         <v>18</v>
       </c>
@@ -3422,8 +3422,8 @@
       </c>
     </row>
     <row r="64" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="21"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="21"/>
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3465,8 +3465,8 @@
       </c>
     </row>
     <row r="65" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="21"/>
-      <c r="B65" s="23"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="21"/>
       <c r="C65" s="1" t="s">
         <v>20</v>
       </c>
@@ -3508,8 +3508,8 @@
       </c>
     </row>
     <row r="66" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="21"/>
-      <c r="B66" s="23"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="21"/>
       <c r="C66" s="1" t="s">
         <v>21</v>
       </c>
@@ -3551,8 +3551,8 @@
       </c>
     </row>
     <row r="67" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="21"/>
-      <c r="B67" s="23"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="21"/>
       <c r="C67" s="1" t="s">
         <v>22</v>
       </c>
@@ -3594,8 +3594,8 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="21"/>
-      <c r="B68" s="23"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="21"/>
       <c r="C68" s="1" t="s">
         <v>23</v>
       </c>
@@ -3637,8 +3637,8 @@
       </c>
     </row>
     <row r="69" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="21"/>
-      <c r="B69" s="23"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="21"/>
       <c r="C69" s="1" t="s">
         <v>24</v>
       </c>
@@ -3680,8 +3680,8 @@
       </c>
     </row>
     <row r="70" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="21"/>
-      <c r="B70" s="23"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="21"/>
       <c r="C70" s="1" t="s">
         <v>25</v>
       </c>
@@ -3723,8 +3723,8 @@
       </c>
     </row>
     <row r="71" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="21"/>
-      <c r="B71" s="23"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="21"/>
       <c r="C71" s="1" t="s">
         <v>26</v>
       </c>
@@ -3766,8 +3766,8 @@
       </c>
     </row>
     <row r="72" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="21"/>
-      <c r="B72" s="23"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="21"/>
       <c r="C72" s="1" t="s">
         <v>27</v>
       </c>
@@ -3809,8 +3809,8 @@
       </c>
     </row>
     <row r="73" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="21"/>
-      <c r="B73" s="23"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="21"/>
       <c r="C73" s="1" t="s">
         <v>28</v>
       </c>
@@ -3852,8 +3852,8 @@
       </c>
     </row>
     <row r="74" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="21"/>
-      <c r="B74" s="23"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="21"/>
       <c r="C74" s="1" t="s">
         <v>29</v>
       </c>
@@ -3895,8 +3895,8 @@
       </c>
     </row>
     <row r="75" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="21"/>
-      <c r="B75" s="23"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="21"/>
       <c r="C75" s="1" t="s">
         <v>30</v>
       </c>
@@ -3938,8 +3938,8 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="21"/>
-      <c r="B76" s="18"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="1" t="s">
         <v>31</v>
       </c>
@@ -3981,8 +3981,8 @@
       </c>
     </row>
     <row r="77" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="21"/>
-      <c r="B77" s="19" t="s">
+      <c r="A77" s="18"/>
+      <c r="B77" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -4026,8 +4026,8 @@
       </c>
     </row>
     <row r="78" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="21"/>
-      <c r="B78" s="23"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="21"/>
       <c r="C78" s="1" t="s">
         <v>18</v>
       </c>
@@ -4069,8 +4069,8 @@
       </c>
     </row>
     <row r="79" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="21"/>
-      <c r="B79" s="23"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="21"/>
       <c r="C79" s="1" t="s">
         <v>19</v>
       </c>
@@ -4112,8 +4112,8 @@
       </c>
     </row>
     <row r="80" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="21"/>
-      <c r="B80" s="23"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="21"/>
       <c r="C80" s="1" t="s">
         <v>20</v>
       </c>
@@ -4155,8 +4155,8 @@
       </c>
     </row>
     <row r="81" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="21"/>
-      <c r="B81" s="23"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="21"/>
       <c r="C81" s="1" t="s">
         <v>21</v>
       </c>
@@ -4198,8 +4198,8 @@
       </c>
     </row>
     <row r="82" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="21"/>
-      <c r="B82" s="23"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="21"/>
       <c r="C82" s="1" t="s">
         <v>22</v>
       </c>
@@ -4241,8 +4241,8 @@
       </c>
     </row>
     <row r="83" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="21"/>
-      <c r="B83" s="23"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="21"/>
       <c r="C83" s="1" t="s">
         <v>23</v>
       </c>
@@ -4284,8 +4284,8 @@
       </c>
     </row>
     <row r="84" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="21"/>
-      <c r="B84" s="23"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="21"/>
       <c r="C84" s="1" t="s">
         <v>24</v>
       </c>
@@ -4327,8 +4327,8 @@
       </c>
     </row>
     <row r="85" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="21"/>
-      <c r="B85" s="23"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="21"/>
       <c r="C85" s="1" t="s">
         <v>25</v>
       </c>
@@ -4370,8 +4370,8 @@
       </c>
     </row>
     <row r="86" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="21"/>
-      <c r="B86" s="23"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="21"/>
       <c r="C86" s="1" t="s">
         <v>26</v>
       </c>
@@ -4413,8 +4413,8 @@
       </c>
     </row>
     <row r="87" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="21"/>
-      <c r="B87" s="23"/>
+      <c r="A87" s="18"/>
+      <c r="B87" s="21"/>
       <c r="C87" s="1" t="s">
         <v>27</v>
       </c>
@@ -4456,8 +4456,8 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="21"/>
-      <c r="B88" s="23"/>
+      <c r="A88" s="18"/>
+      <c r="B88" s="21"/>
       <c r="C88" s="1" t="s">
         <v>28</v>
       </c>
@@ -4499,8 +4499,8 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="21"/>
-      <c r="B89" s="23"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="21"/>
       <c r="C89" s="1" t="s">
         <v>29</v>
       </c>
@@ -4542,8 +4542,8 @@
       </c>
     </row>
     <row r="90" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="21"/>
-      <c r="B90" s="23"/>
+      <c r="A90" s="18"/>
+      <c r="B90" s="21"/>
       <c r="C90" s="1" t="s">
         <v>30</v>
       </c>
@@ -4585,8 +4585,8 @@
       </c>
     </row>
     <row r="91" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="22"/>
-      <c r="B91" s="18"/>
+      <c r="A91" s="19"/>
+      <c r="B91" s="22"/>
       <c r="C91" s="1" t="s">
         <v>31</v>
       </c>
@@ -4628,10 +4628,10 @@
       </c>
     </row>
     <row r="92" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20">
+      <c r="A92" s="17">
         <v>2026</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4675,8 +4675,8 @@
       </c>
     </row>
     <row r="93" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="21"/>
-      <c r="B93" s="23"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="21"/>
       <c r="C93" s="1" t="s">
         <v>18</v>
       </c>
@@ -4718,8 +4718,8 @@
       </c>
     </row>
     <row r="94" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="21"/>
-      <c r="B94" s="23"/>
+      <c r="A94" s="18"/>
+      <c r="B94" s="21"/>
       <c r="C94" s="1" t="s">
         <v>19</v>
       </c>
@@ -4761,8 +4761,8 @@
       </c>
     </row>
     <row r="95" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="21"/>
-      <c r="B95" s="23"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="21"/>
       <c r="C95" s="1" t="s">
         <v>20</v>
       </c>
@@ -4804,8 +4804,8 @@
       </c>
     </row>
     <row r="96" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="21"/>
-      <c r="B96" s="23"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="21"/>
       <c r="C96" s="1" t="s">
         <v>21</v>
       </c>
@@ -4847,8 +4847,8 @@
       </c>
     </row>
     <row r="97" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="21"/>
-      <c r="B97" s="23"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="21"/>
       <c r="C97" s="1" t="s">
         <v>22</v>
       </c>
@@ -4890,8 +4890,8 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="21"/>
-      <c r="B98" s="23"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="21"/>
       <c r="C98" s="1" t="s">
         <v>23</v>
       </c>
@@ -4933,8 +4933,8 @@
       </c>
     </row>
     <row r="99" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="21"/>
-      <c r="B99" s="23"/>
+      <c r="A99" s="18"/>
+      <c r="B99" s="21"/>
       <c r="C99" s="1" t="s">
         <v>24</v>
       </c>
@@ -4976,8 +4976,8 @@
       </c>
     </row>
     <row r="100" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="21"/>
-      <c r="B100" s="23"/>
+      <c r="A100" s="18"/>
+      <c r="B100" s="21"/>
       <c r="C100" s="1" t="s">
         <v>25</v>
       </c>
@@ -5019,8 +5019,8 @@
       </c>
     </row>
     <row r="101" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="21"/>
-      <c r="B101" s="23"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="21"/>
       <c r="C101" s="1" t="s">
         <v>26</v>
       </c>
@@ -5062,8 +5062,8 @@
       </c>
     </row>
     <row r="102" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="21"/>
-      <c r="B102" s="23"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="21"/>
       <c r="C102" s="1" t="s">
         <v>27</v>
       </c>
@@ -5105,8 +5105,8 @@
       </c>
     </row>
     <row r="103" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="21"/>
-      <c r="B103" s="23"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="21"/>
       <c r="C103" s="1" t="s">
         <v>28</v>
       </c>
@@ -5148,8 +5148,8 @@
       </c>
     </row>
     <row r="104" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="21"/>
-      <c r="B104" s="23"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="21"/>
       <c r="C104" s="1" t="s">
         <v>29</v>
       </c>
@@ -5191,8 +5191,8 @@
       </c>
     </row>
     <row r="105" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="21"/>
-      <c r="B105" s="23"/>
+      <c r="A105" s="18"/>
+      <c r="B105" s="21"/>
       <c r="C105" s="1" t="s">
         <v>30</v>
       </c>
@@ -5234,8 +5234,8 @@
       </c>
     </row>
     <row r="106" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="21"/>
-      <c r="B106" s="18"/>
+      <c r="A106" s="18"/>
+      <c r="B106" s="22"/>
       <c r="C106" s="13" t="s">
         <v>31</v>
       </c>
@@ -5277,8 +5277,8 @@
       </c>
     </row>
     <row r="107" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="21"/>
-      <c r="B107" s="19" t="s">
+      <c r="A107" s="18"/>
+      <c r="B107" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -5322,8 +5322,8 @@
       </c>
     </row>
     <row r="108" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="21"/>
-      <c r="B108" s="23"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="21"/>
       <c r="C108" s="1" t="s">
         <v>18</v>
       </c>
@@ -5365,8 +5365,8 @@
       </c>
     </row>
     <row r="109" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="21"/>
-      <c r="B109" s="23"/>
+      <c r="A109" s="18"/>
+      <c r="B109" s="21"/>
       <c r="C109" s="1" t="s">
         <v>19</v>
       </c>
@@ -5408,8 +5408,8 @@
       </c>
     </row>
     <row r="110" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="21"/>
-      <c r="B110" s="23"/>
+      <c r="A110" s="18"/>
+      <c r="B110" s="21"/>
       <c r="C110" s="1" t="s">
         <v>20</v>
       </c>
@@ -5451,8 +5451,8 @@
       </c>
     </row>
     <row r="111" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="21"/>
-      <c r="B111" s="23"/>
+      <c r="A111" s="18"/>
+      <c r="B111" s="21"/>
       <c r="C111" s="1" t="s">
         <v>21</v>
       </c>
@@ -5494,8 +5494,8 @@
       </c>
     </row>
     <row r="112" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="21"/>
-      <c r="B112" s="23"/>
+      <c r="A112" s="18"/>
+      <c r="B112" s="21"/>
       <c r="C112" s="1" t="s">
         <v>22</v>
       </c>
@@ -5537,8 +5537,8 @@
       </c>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="21"/>
-      <c r="B113" s="23"/>
+      <c r="A113" s="18"/>
+      <c r="B113" s="21"/>
       <c r="C113" s="1" t="s">
         <v>23</v>
       </c>
@@ -5580,8 +5580,8 @@
       </c>
     </row>
     <row r="114" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="21"/>
-      <c r="B114" s="23"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="21"/>
       <c r="C114" s="1" t="s">
         <v>24</v>
       </c>
@@ -5623,8 +5623,8 @@
       </c>
     </row>
     <row r="115" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="21"/>
-      <c r="B115" s="23"/>
+      <c r="A115" s="18"/>
+      <c r="B115" s="21"/>
       <c r="C115" s="1" t="s">
         <v>25</v>
       </c>
@@ -5666,8 +5666,8 @@
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="21"/>
-      <c r="B116" s="23"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="21"/>
       <c r="C116" s="1" t="s">
         <v>26</v>
       </c>
@@ -5709,8 +5709,8 @@
       </c>
     </row>
     <row r="117" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="21"/>
-      <c r="B117" s="23"/>
+      <c r="A117" s="18"/>
+      <c r="B117" s="21"/>
       <c r="C117" s="1" t="s">
         <v>27</v>
       </c>
@@ -5752,8 +5752,8 @@
       </c>
     </row>
     <row r="118" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="21"/>
-      <c r="B118" s="23"/>
+      <c r="A118" s="18"/>
+      <c r="B118" s="21"/>
       <c r="C118" s="1" t="s">
         <v>28</v>
       </c>
@@ -5795,8 +5795,8 @@
       </c>
     </row>
     <row r="119" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="21"/>
-      <c r="B119" s="23"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="21"/>
       <c r="C119" s="1" t="s">
         <v>29</v>
       </c>
@@ -5838,8 +5838,8 @@
       </c>
     </row>
     <row r="120" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="21"/>
-      <c r="B120" s="23"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="21"/>
       <c r="C120" s="1" t="s">
         <v>30</v>
       </c>
@@ -5881,8 +5881,8 @@
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="22"/>
-      <c r="B121" s="18"/>
+      <c r="A121" s="19"/>
+      <c r="B121" s="22"/>
       <c r="C121" s="13" t="s">
         <v>31</v>
       </c>

--- a/officepro_direccion.xlsx
+++ b/officepro_direccion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\code\_other\datos-officepro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED07765E-2E3D-46F7-A6F2-6995A466D9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6021ABC6-700B-44A9-A29C-7AD57B5FE86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14655" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,16 +680,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="15" width="8.88671875" style="1" customWidth="1"/>
-    <col min="16" max="17" width="8.88671875" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">

--- a/officepro_direccion.xlsx
+++ b/officepro_direccion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\code\_other\datos-officepro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6021ABC6-700B-44A9-A29C-7AD57B5FE86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698704AD-96C5-47B4-9695-BE2D8C5FDC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14655" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,7 +681,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O121"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" bestFit="1" customWidth="1"/>
